--- a/data/庫存股票.xlsx
+++ b/data/庫存股票.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\每日收盤\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\GitHub_Clone\stock-dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E058C0D8-BEEB-47BA-A27F-9958984B57CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F7A159-A8E7-4673-8FD2-A1F20C1983D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{650CFE38-EEF9-4EED-A741-4EDFC6963903}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="23">
   <si>
     <t>股票名稱</t>
   </si>
@@ -1079,7 +1079,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCA7DE10-CAE2-46DA-8E9E-694D11448EA0}">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -1991,6 +1991,26 @@
         <v>58.05</v>
       </c>
     </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>21</v>
+      </c>
+      <c r="B46">
+        <v>100</v>
+      </c>
+      <c r="C46">
+        <v>2950</v>
+      </c>
+      <c r="D46" s="1">
+        <v>46260</v>
+      </c>
+      <c r="E46">
+        <v>20</v>
+      </c>
+      <c r="G46">
+        <v>2950</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/庫存股票.xlsx
+++ b/data/庫存股票.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\GitHub_Clone\stock-dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F7A159-A8E7-4673-8FD2-A1F20C1983D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE2A4E87-535B-4BFF-A138-7FFFA02B623D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{650CFE38-EEF9-4EED-A741-4EDFC6963903}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="23">
   <si>
     <t>股票名稱</t>
   </si>
@@ -1079,7 +1079,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCA7DE10-CAE2-46DA-8E9E-694D11448EA0}">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -1476,538 +1476,618 @@
         <v>12</v>
       </c>
       <c r="B20">
-        <v>57000</v>
+        <v>5000</v>
       </c>
       <c r="C20">
-        <v>23.38</v>
+        <v>23.32</v>
       </c>
       <c r="D20" s="1">
-        <v>46024</v>
+        <v>46098</v>
       </c>
       <c r="E20">
         <v>15</v>
       </c>
       <c r="G20">
-        <v>23.38</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B21">
-        <v>100</v>
+        <v>10000</v>
       </c>
       <c r="C21">
-        <v>1245</v>
+        <v>30.66</v>
       </c>
       <c r="D21" s="1">
-        <v>45673</v>
+        <v>46188</v>
       </c>
       <c r="E21">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G21">
-        <v>1245</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B22">
-        <v>50</v>
+        <v>40000</v>
       </c>
       <c r="C22">
-        <v>2040</v>
+        <v>22.68</v>
       </c>
       <c r="D22" s="1">
-        <v>46013</v>
+        <v>46024</v>
       </c>
       <c r="E22">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G22">
-        <v>2040</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B23">
-        <v>200</v>
+        <v>3000</v>
       </c>
       <c r="C23">
-        <v>818</v>
+        <v>32.69</v>
       </c>
       <c r="D23" s="1">
-        <v>45918</v>
+        <v>46280</v>
       </c>
       <c r="E23">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G23">
-        <v>818</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B24">
-        <v>100</v>
+        <v>12000</v>
       </c>
       <c r="C24">
-        <v>829</v>
+        <v>25.67</v>
       </c>
       <c r="D24" s="1">
-        <v>45923</v>
+        <v>45550</v>
       </c>
       <c r="E24">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G24">
-        <v>829</v>
+        <v>25.67</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B25">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="C25">
-        <v>1915</v>
+        <v>1245</v>
       </c>
       <c r="D25" s="1">
-        <v>46100</v>
+        <v>45673</v>
       </c>
       <c r="E25">
         <v>20</v>
       </c>
       <c r="G25">
-        <v>1915</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B26">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="C26">
-        <v>968</v>
+        <v>2040</v>
       </c>
       <c r="D26" s="1">
-        <v>46092</v>
+        <v>46013</v>
       </c>
       <c r="E26">
         <v>20</v>
       </c>
       <c r="G26">
-        <v>968</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B27">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="C27">
-        <v>918</v>
+        <v>818</v>
       </c>
       <c r="D27" s="1">
-        <v>46112</v>
+        <v>45918</v>
       </c>
       <c r="E27">
         <v>20</v>
       </c>
       <c r="G27">
-        <v>918</v>
+        <v>818</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B28">
         <v>100</v>
       </c>
       <c r="C28">
-        <v>945</v>
+        <v>829</v>
       </c>
       <c r="D28" s="1">
-        <v>46162</v>
+        <v>45923</v>
       </c>
       <c r="E28">
         <v>20</v>
       </c>
       <c r="G28">
-        <v>945</v>
+        <v>829</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B29">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="C29">
-        <v>3345</v>
+        <v>1915</v>
       </c>
       <c r="D29" s="1">
-        <v>46090</v>
+        <v>46100</v>
       </c>
       <c r="E29">
         <v>20</v>
       </c>
       <c r="G29">
-        <v>3345</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B30">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="C30">
-        <v>3165</v>
+        <v>968</v>
       </c>
       <c r="D30" s="1">
-        <v>46105</v>
+        <v>46092</v>
       </c>
       <c r="E30">
         <v>20</v>
       </c>
       <c r="G30">
-        <v>3165</v>
+        <v>968</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B31">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C31">
-        <v>3150</v>
+        <v>918</v>
       </c>
       <c r="D31" s="1">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="E31">
         <v>20</v>
       </c>
       <c r="G31">
-        <v>3150</v>
+        <v>918</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B32">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C32">
-        <v>3120</v>
+        <v>945</v>
       </c>
       <c r="D32" s="1">
-        <v>46112</v>
+        <v>46162</v>
       </c>
       <c r="E32">
         <v>20</v>
       </c>
       <c r="G32">
-        <v>3120</v>
+        <v>945</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B33">
-        <v>20000</v>
+        <v>50</v>
       </c>
       <c r="C33">
-        <v>11.32</v>
+        <v>3345</v>
       </c>
       <c r="D33" s="1">
-        <v>46024</v>
+        <v>46090</v>
       </c>
       <c r="E33">
         <v>20</v>
       </c>
       <c r="G33">
-        <v>11.32</v>
+        <v>3345</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B34">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="C34">
-        <v>881.75</v>
+        <v>3165</v>
       </c>
       <c r="D34" s="1">
-        <v>46146</v>
+        <v>46105</v>
       </c>
       <c r="E34">
         <v>20</v>
       </c>
       <c r="G34">
-        <v>881.75</v>
+        <v>3165</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B35">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="C35">
-        <v>1780</v>
+        <v>3150</v>
       </c>
       <c r="D35" s="1">
-        <v>46156</v>
+        <v>46108</v>
       </c>
       <c r="E35">
         <v>20</v>
       </c>
       <c r="G35">
-        <v>1780</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B36">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C36">
-        <v>1610</v>
+        <v>3120</v>
       </c>
       <c r="D36" s="1">
-        <v>46161</v>
+        <v>46112</v>
       </c>
       <c r="E36">
         <v>20</v>
       </c>
       <c r="G36">
-        <v>1610</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B37">
-        <v>100</v>
+        <v>20000</v>
       </c>
       <c r="C37">
-        <v>1930</v>
+        <v>11.32</v>
       </c>
       <c r="D37" s="1">
-        <v>46161</v>
+        <v>46024</v>
       </c>
       <c r="E37">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G37">
-        <v>1930</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B38">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="C38">
-        <v>3395</v>
+        <v>881.75</v>
       </c>
       <c r="D38" s="1">
-        <v>46169</v>
+        <v>46146</v>
       </c>
       <c r="E38">
         <v>20</v>
       </c>
       <c r="G38">
-        <v>3395</v>
+        <v>881.75</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B39">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="C39">
-        <v>3210</v>
+        <v>1780</v>
       </c>
       <c r="D39" s="1">
-        <v>46171</v>
+        <v>46156</v>
       </c>
       <c r="E39">
         <v>20</v>
       </c>
       <c r="G39">
-        <v>3210</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B40">
         <v>100</v>
       </c>
       <c r="C40">
-        <v>3130</v>
+        <v>1610</v>
       </c>
       <c r="D40" s="1">
-        <v>46182</v>
+        <v>46161</v>
       </c>
       <c r="E40">
         <v>20</v>
       </c>
       <c r="G40">
-        <v>3130</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B41">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="C41">
-        <v>30.66</v>
+        <v>1930</v>
       </c>
       <c r="D41" s="1">
-        <v>46188</v>
+        <v>46161</v>
       </c>
       <c r="E41">
         <v>15</v>
       </c>
       <c r="G41">
-        <v>30.66</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B42">
         <v>100</v>
       </c>
       <c r="C42">
-        <v>2000</v>
+        <v>3395</v>
       </c>
       <c r="D42" s="1">
-        <v>46197</v>
+        <v>46169</v>
       </c>
       <c r="E42">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G42">
-        <v>2000</v>
+        <v>3395</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B43">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="C43">
-        <v>675</v>
+        <v>3210</v>
       </c>
       <c r="D43" s="1">
-        <v>46197</v>
+        <v>46171</v>
       </c>
       <c r="E43">
         <v>20</v>
       </c>
       <c r="G43">
-        <v>675</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B44">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="C44">
-        <v>580</v>
+        <v>3130</v>
       </c>
       <c r="D44" s="1">
-        <v>46199</v>
+        <v>46182</v>
       </c>
       <c r="E44">
         <v>20</v>
       </c>
       <c r="G44">
-        <v>580</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B45">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="C45">
-        <v>58.05</v>
+        <v>30.66</v>
       </c>
       <c r="D45" s="1">
-        <v>46310</v>
+        <v>46188</v>
       </c>
       <c r="E45">
         <v>15</v>
       </c>
       <c r="G45">
-        <v>58.05</v>
+        <v>30.66</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>20</v>
+      </c>
+      <c r="B46">
+        <v>100</v>
+      </c>
+      <c r="C46">
+        <v>2000</v>
+      </c>
+      <c r="D46" s="1">
+        <v>46197</v>
+      </c>
+      <c r="E46">
+        <v>15</v>
+      </c>
+      <c r="G46">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>22</v>
+      </c>
+      <c r="B47">
+        <v>300</v>
+      </c>
+      <c r="C47">
+        <v>675</v>
+      </c>
+      <c r="D47" s="1">
+        <v>46197</v>
+      </c>
+      <c r="E47">
+        <v>20</v>
+      </c>
+      <c r="G47">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>22</v>
+      </c>
+      <c r="B48">
+        <v>200</v>
+      </c>
+      <c r="C48">
+        <v>580</v>
+      </c>
+      <c r="D48" s="1">
+        <v>46199</v>
+      </c>
+      <c r="E48">
+        <v>20</v>
+      </c>
+      <c r="G48">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>11</v>
+      </c>
+      <c r="B49">
+        <v>1000</v>
+      </c>
+      <c r="C49">
+        <v>58.05</v>
+      </c>
+      <c r="D49" s="1">
+        <v>46310</v>
+      </c>
+      <c r="E49">
+        <v>15</v>
+      </c>
+      <c r="G49">
+        <v>58.05</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>21</v>
       </c>
-      <c r="B46">
-        <v>100</v>
-      </c>
-      <c r="C46">
+      <c r="B50">
+        <v>100</v>
+      </c>
+      <c r="C50">
         <v>2950</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D50" s="1">
         <v>46260</v>
       </c>
-      <c r="E46">
-        <v>20</v>
-      </c>
-      <c r="G46">
+      <c r="E50">
+        <v>20</v>
+      </c>
+      <c r="G50">
         <v>2950</v>
       </c>
     </row>

--- a/data/庫存股票.xlsx
+++ b/data/庫存股票.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\GitHub_Clone\stock-dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE2A4E87-535B-4BFF-A138-7FFFA02B623D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1781B41A-BCF4-40DB-B164-3A476212C085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{650CFE38-EEF9-4EED-A741-4EDFC6963903}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="23">
   <si>
     <t>股票名稱</t>
   </si>
@@ -1079,7 +1079,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCA7DE10-CAE2-46DA-8E9E-694D11448EA0}">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -1553,22 +1553,22 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B24">
-        <v>12000</v>
+        <v>100</v>
       </c>
       <c r="C24">
-        <v>25.67</v>
+        <v>1245</v>
       </c>
       <c r="D24" s="1">
-        <v>45550</v>
+        <v>45673</v>
       </c>
       <c r="E24">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G24">
-        <v>25.67</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -1576,39 +1576,39 @@
         <v>13</v>
       </c>
       <c r="B25">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C25">
-        <v>1245</v>
+        <v>2040</v>
       </c>
       <c r="D25" s="1">
-        <v>45673</v>
+        <v>46013</v>
       </c>
       <c r="E25">
         <v>20</v>
       </c>
       <c r="G25">
-        <v>1245</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B26">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="C26">
-        <v>2040</v>
+        <v>818</v>
       </c>
       <c r="D26" s="1">
-        <v>46013</v>
+        <v>45918</v>
       </c>
       <c r="E26">
         <v>20</v>
       </c>
       <c r="G26">
-        <v>2040</v>
+        <v>818</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -1616,19 +1616,19 @@
         <v>14</v>
       </c>
       <c r="B27">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="C27">
-        <v>818</v>
+        <v>829</v>
       </c>
       <c r="D27" s="1">
-        <v>45918</v>
+        <v>45923</v>
       </c>
       <c r="E27">
         <v>20</v>
       </c>
       <c r="G27">
-        <v>818</v>
+        <v>829</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -1636,39 +1636,39 @@
         <v>14</v>
       </c>
       <c r="B28">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="C28">
-        <v>829</v>
+        <v>1915</v>
       </c>
       <c r="D28" s="1">
-        <v>45923</v>
+        <v>46100</v>
       </c>
       <c r="E28">
         <v>20</v>
       </c>
       <c r="G28">
-        <v>829</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B29">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="C29">
-        <v>1915</v>
+        <v>968</v>
       </c>
       <c r="D29" s="1">
-        <v>46100</v>
+        <v>46092</v>
       </c>
       <c r="E29">
         <v>20</v>
       </c>
       <c r="G29">
-        <v>1915</v>
+        <v>968</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -1676,19 +1676,19 @@
         <v>15</v>
       </c>
       <c r="B30">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="C30">
-        <v>968</v>
+        <v>918</v>
       </c>
       <c r="D30" s="1">
-        <v>46092</v>
+        <v>46112</v>
       </c>
       <c r="E30">
         <v>20</v>
       </c>
       <c r="G30">
-        <v>968</v>
+        <v>918</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -1699,36 +1699,36 @@
         <v>100</v>
       </c>
       <c r="C31">
-        <v>918</v>
+        <v>945</v>
       </c>
       <c r="D31" s="1">
-        <v>46112</v>
+        <v>46162</v>
       </c>
       <c r="E31">
         <v>20</v>
       </c>
       <c r="G31">
-        <v>918</v>
+        <v>945</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B32">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C32">
-        <v>945</v>
+        <v>3345</v>
       </c>
       <c r="D32" s="1">
-        <v>46162</v>
+        <v>46090</v>
       </c>
       <c r="E32">
         <v>20</v>
       </c>
       <c r="G32">
-        <v>945</v>
+        <v>3345</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -1739,16 +1739,16 @@
         <v>50</v>
       </c>
       <c r="C33">
-        <v>3345</v>
+        <v>3165</v>
       </c>
       <c r="D33" s="1">
-        <v>46090</v>
+        <v>46105</v>
       </c>
       <c r="E33">
         <v>20</v>
       </c>
       <c r="G33">
-        <v>3345</v>
+        <v>3165</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -1759,16 +1759,16 @@
         <v>50</v>
       </c>
       <c r="C34">
-        <v>3165</v>
+        <v>3150</v>
       </c>
       <c r="D34" s="1">
-        <v>46105</v>
+        <v>46108</v>
       </c>
       <c r="E34">
         <v>20</v>
       </c>
       <c r="G34">
-        <v>3165</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -1779,76 +1779,76 @@
         <v>50</v>
       </c>
       <c r="C35">
-        <v>3150</v>
+        <v>3120</v>
       </c>
       <c r="D35" s="1">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="E35">
         <v>20</v>
       </c>
       <c r="G35">
-        <v>3150</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B36">
-        <v>50</v>
+        <v>20000</v>
       </c>
       <c r="C36">
-        <v>3120</v>
+        <v>11.32</v>
       </c>
       <c r="D36" s="1">
-        <v>46112</v>
+        <v>46024</v>
       </c>
       <c r="E36">
         <v>20</v>
       </c>
       <c r="G36">
-        <v>3120</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B37">
-        <v>20000</v>
+        <v>1000</v>
       </c>
       <c r="C37">
-        <v>11.32</v>
+        <v>881.75</v>
       </c>
       <c r="D37" s="1">
-        <v>46024</v>
+        <v>46146</v>
       </c>
       <c r="E37">
         <v>20</v>
       </c>
       <c r="G37">
-        <v>11.32</v>
+        <v>881.75</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B38">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="C38">
-        <v>881.75</v>
+        <v>1780</v>
       </c>
       <c r="D38" s="1">
-        <v>46146</v>
+        <v>46156</v>
       </c>
       <c r="E38">
         <v>20</v>
       </c>
       <c r="G38">
-        <v>881.75</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -1856,59 +1856,59 @@
         <v>19</v>
       </c>
       <c r="B39">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="C39">
-        <v>1780</v>
+        <v>1610</v>
       </c>
       <c r="D39" s="1">
-        <v>46156</v>
+        <v>46161</v>
       </c>
       <c r="E39">
         <v>20</v>
       </c>
       <c r="G39">
-        <v>1780</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B40">
         <v>100</v>
       </c>
       <c r="C40">
-        <v>1610</v>
+        <v>1930</v>
       </c>
       <c r="D40" s="1">
         <v>46161</v>
       </c>
       <c r="E40">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G40">
-        <v>1610</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B41">
         <v>100</v>
       </c>
       <c r="C41">
-        <v>1930</v>
+        <v>3395</v>
       </c>
       <c r="D41" s="1">
-        <v>46161</v>
+        <v>46169</v>
       </c>
       <c r="E41">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G41">
-        <v>1930</v>
+        <v>3395</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -1919,96 +1919,96 @@
         <v>100</v>
       </c>
       <c r="C42">
-        <v>3395</v>
+        <v>3210</v>
       </c>
       <c r="D42" s="1">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="E42">
         <v>20</v>
       </c>
       <c r="G42">
-        <v>3395</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B43">
         <v>100</v>
       </c>
       <c r="C43">
-        <v>3210</v>
+        <v>3130</v>
       </c>
       <c r="D43" s="1">
-        <v>46171</v>
+        <v>46182</v>
       </c>
       <c r="E43">
         <v>20</v>
       </c>
       <c r="G43">
-        <v>3210</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B44">
-        <v>100</v>
+        <v>12000</v>
       </c>
       <c r="C44">
-        <v>3130</v>
+        <v>25.67</v>
       </c>
       <c r="D44" s="1">
-        <v>46182</v>
+        <v>46188</v>
       </c>
       <c r="E44">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G44">
-        <v>3130</v>
+        <v>25.67</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B45">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="C45">
-        <v>30.66</v>
+        <v>2000</v>
       </c>
       <c r="D45" s="1">
-        <v>46188</v>
+        <v>46197</v>
       </c>
       <c r="E45">
         <v>15</v>
       </c>
       <c r="G45">
-        <v>30.66</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B46">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="C46">
-        <v>2000</v>
+        <v>675</v>
       </c>
       <c r="D46" s="1">
         <v>46197</v>
       </c>
       <c r="E46">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G46">
-        <v>2000</v>
+        <v>675</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -2016,78 +2016,58 @@
         <v>22</v>
       </c>
       <c r="B47">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="C47">
-        <v>675</v>
+        <v>580</v>
       </c>
       <c r="D47" s="1">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="E47">
         <v>20</v>
       </c>
       <c r="G47">
-        <v>675</v>
+        <v>580</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B48">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="C48">
-        <v>580</v>
+        <v>58.05</v>
       </c>
       <c r="D48" s="1">
-        <v>46199</v>
+        <v>46310</v>
       </c>
       <c r="E48">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G48">
-        <v>580</v>
+        <v>58.05</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B49">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="C49">
-        <v>58.05</v>
+        <v>2950</v>
       </c>
       <c r="D49" s="1">
-        <v>46310</v>
+        <v>46260</v>
       </c>
       <c r="E49">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G49">
-        <v>58.05</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>21</v>
-      </c>
-      <c r="B50">
-        <v>100</v>
-      </c>
-      <c r="C50">
-        <v>2950</v>
-      </c>
-      <c r="D50" s="1">
-        <v>46260</v>
-      </c>
-      <c r="E50">
-        <v>20</v>
-      </c>
-      <c r="G50">
         <v>2950</v>
       </c>
     </row>
